--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_region2.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_region2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <r>
       <rPr>
@@ -321,6 +321,28 @@
   </si>
   <si>
     <t>保险费</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>国家</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1459,18 +1481,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:2">
+    <row r="1" s="1" customFormat="1" ht="26" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_region2.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplate_region2.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="分区城市" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -149,26 +149,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>失效日期</t>
-    </r>
+    <t>失效日期</t>
   </si>
   <si>
     <r>
@@ -1410,7 +1391,7 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1467,7 +1448,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
       <formula1>"0.01  保留两位小数四金五入,0.1  保留一位小数四舍五入,0  向下取整，小数舍弃,0.5  0.5进制,1  向上取整，小数进1,2  保留整数，四舍五入"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G$1:G$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G2:G1048576">
       <formula1>32874</formula1>
       <formula2>398117</formula2>
     </dataValidation>
